--- a/Products.xlsx
+++ b/Products.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Programming\Projects\Guessing_Perfume\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohamed\Desktop\Work\Perfamix Quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7D6837-03C7-4CD5-A884-0920E99B5652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_21F70FD57EA883672819CCD55D0616FC16E85506" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$172</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="694">
   <si>
     <t>ID</t>
   </si>
@@ -61,7 +61,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Black-Code-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Black-Code/</t>
+    <t>https://perfamix.com/product/black-code/</t>
   </si>
   <si>
     <t>Amour</t>
@@ -76,7 +76,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Amour-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Amour/</t>
+    <t>https://perfamix.com/product/amour/</t>
   </si>
   <si>
     <t>Bonded</t>
@@ -88,7 +88,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Bonded-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Bonded/</t>
+    <t>https://perfamix.com/product/bonded/</t>
   </si>
   <si>
     <t>Divine Kiss</t>
@@ -100,7 +100,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Divine-Kiss-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Divine-Kiss/</t>
+    <t>https://perfamix.com/product/divine-kiss/</t>
   </si>
   <si>
     <t>Elite</t>
@@ -112,7 +112,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Elite-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Elite/</t>
+    <t>https://perfamix.com/product/elite/</t>
   </si>
   <si>
     <t>FreshVibe</t>
@@ -127,7 +127,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/FreshVibe-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/FreshVibe/</t>
+    <t>https://perfamix.com/product/freshvibe/</t>
   </si>
   <si>
     <t>Honey Scent</t>
@@ -139,7 +139,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Honey-Scent-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Honey-Scent/</t>
+    <t>https://perfamix.com/product/honey-scent/</t>
   </si>
   <si>
     <t>Hudson Valley</t>
@@ -151,7 +151,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Hudson-Valley-Gissah-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Hudson-Valley/</t>
+    <t>https://perfamix.com/product/hudson-valley/</t>
   </si>
   <si>
     <t>Scent Aura</t>
@@ -163,7 +163,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Scent-Aura-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Scent-Aura/</t>
+    <t>https://perfamix.com/product/scent-aura/</t>
   </si>
   <si>
     <t>ShowMix</t>
@@ -175,7 +175,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/ShowMix-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/ShowMix/</t>
+    <t>https://perfamix.com/product/showmix/</t>
   </si>
   <si>
     <t>Veloura</t>
@@ -187,7 +187,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Veloura-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Veloura/</t>
+    <t>https://perfamix.com/product/veloura/</t>
   </si>
   <si>
     <t>Velvet Sugar</t>
@@ -199,7 +199,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Velvet-Sugar-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Velvet-Sugar/</t>
+    <t>https://perfamix.com/product/velvet-sugar/</t>
   </si>
   <si>
     <t>Oud Wood</t>
@@ -211,7 +211,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Oud-Wood-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Oud-Wood/</t>
+    <t>https://perfamix.com/product/oud-wood/</t>
   </si>
   <si>
     <t>Dark Aura</t>
@@ -223,7 +223,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Dark-Aura-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Dark-Aura/</t>
+    <t>https://perfamix.com/product/dark-aura/</t>
   </si>
   <si>
     <t>Lollipop</t>
@@ -235,7 +235,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Lollipop-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Lollipop/</t>
+    <t>https://perfamix.com/product/lollipop/</t>
   </si>
   <si>
     <t>Golden Vanilla</t>
@@ -247,7 +247,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Golden-Vanilla-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Golden-Vanilla/</t>
+    <t>https://perfamix.com/product/golden-vanilla/</t>
   </si>
   <si>
     <t>Fruity Twist</t>
@@ -259,7 +259,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Fruity-Twist-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Fruity-Twist/</t>
+    <t>https://perfamix.com/product/fruity-twist/</t>
   </si>
   <si>
     <t>Amber Chocolate</t>
@@ -271,7 +271,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Amber-Chocolate-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Amber-Chocolate/</t>
+    <t>https://perfamix.com/product/amber-chocolate/</t>
   </si>
   <si>
     <t>Spicy Oud</t>
@@ -283,7 +283,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Spicy-Oud-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Spicy-Oud/</t>
+    <t>https://perfamix.com/product/spicy-oud/</t>
   </si>
   <si>
     <t>Rose Tobacco</t>
@@ -295,7 +295,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/07/Rose-Tobacco-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Rose-Tobacco/</t>
+    <t>https://perfamix.com/product/rose-tobacco/</t>
   </si>
   <si>
     <t>1 Million Lucky Rabanne</t>
@@ -307,7 +307,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/1-Million-Lucky-Rabanne-2.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/1-Million-Lucky-Rabanne/</t>
+    <t>https://perfamix.com/product/1-million-lucky-rabanne/</t>
   </si>
   <si>
     <t>1 Million Prive Rabanne</t>
@@ -322,7 +322,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/1-Million-Prive-2.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/1-Million-Prive-Rabanne/</t>
+    <t>https://perfamix.com/product/1-million-prive-rabanne/</t>
   </si>
   <si>
     <t>1 Million Rabanne</t>
@@ -334,7 +334,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/1-Million-Rabanne-2.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/1-Million-Rabanne/</t>
+    <t>https://perfamix.com/product/1-million-rabanne/</t>
   </si>
   <si>
     <t>212 Sexy Carolina Herrera</t>
@@ -346,7 +346,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/212-Sexy-Carolina-Herrera-2.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/212-Sexy-Carolina-Herrera/</t>
+    <t>https://perfamix.com/product/212-sexy-carolina-herrera/</t>
   </si>
   <si>
     <t>212 Sexy Men Carolina Herrera</t>
@@ -358,7 +358,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/212-Sexy-Men-Carolina-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/212-Sexy-Men-Carolina-Herrera/</t>
+    <t>https://perfamix.com/product/212-sexy-men-carolina-herrera/</t>
   </si>
   <si>
     <t>Acqua di Gio Giorgio Armani</t>
@@ -370,7 +370,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Acqua-di-Gio-Giorgio-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Acqua-di-Gio-Giorgio-Armani/</t>
+    <t>https://perfamix.com/product/acqua-di-gio-giorgio-armani/</t>
   </si>
   <si>
     <t>Acqua di Gio Profumo Giorgio Armani</t>
@@ -382,7 +382,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Acqua-di-Gio-Giorgio-1-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Acqua-di-Gio-Profumo-Giorgio-Armani/</t>
+    <t>https://perfamix.com/product/acqua-di-gio-profumo-giorgio-armani/</t>
   </si>
   <si>
     <t>Alexandria II Xerjoff</t>
@@ -394,7 +394,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Alexandria-II-Xerjoff-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Alexandria-II-Xerjoff/</t>
+    <t>https://perfamix.com/product/alexandria-ii-xerjoff/</t>
   </si>
   <si>
     <t>Alien Mugler</t>
@@ -406,7 +406,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Alien-Mugler-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Alien-Mugler/</t>
+    <t>https://perfamix.com/product/alien-mugler/</t>
   </si>
   <si>
     <t>Allure Homme Sport Chanel</t>
@@ -418,7 +418,10 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Allure-Homme-Sport-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Allure-Homme-Sport-Chanel/</t>
+    <t>https://perfamix.com/product/allure-homme-sport-chanel/</t>
+  </si>
+  <si>
+    <t>Althair Parfums de Marly</t>
   </si>
   <si>
     <t>Althaïr is a rich oriental-vanilla fragrance for men, blending warm cinnamon, cardamom and orange blossom with smooth Bourbon vanilla and elemi. Praline, tonka, candied almond, musk and guaiac wood create a creamy, sweet and sophisticated finish.</t>
@@ -427,6 +430,9 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Althair-Parfums-de-Marly-1.jpg</t>
   </si>
   <si>
+    <t>https://perfamix.com/product/althair-parfums-de-marly/</t>
+  </si>
+  <si>
     <t>Ameerat Al Arab Asdaaf</t>
   </si>
   <si>
@@ -436,7 +442,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Ameerat-Al-Arab-Asdaaf-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Ameerat-Al-Arab-Asdaaf/</t>
+    <t>https://perfamix.com/product/ameerat-al-arab-asdaaf/</t>
   </si>
   <si>
     <t>Angels Share By Kilian</t>
@@ -448,7 +454,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Angels-Share-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Angels-Share-By-Kilian/</t>
+    <t>https://perfamix.com/product/angels-share-by-kilian/</t>
   </si>
   <si>
     <t>Asad Lattafa Perfumes</t>
@@ -460,7 +466,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Asad-Lattafa-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Asad-Lattafa-Perfumes/</t>
+    <t>https://perfamix.com/product/asad-lattafa-perfumes/</t>
   </si>
   <si>
     <t>Asad Zanzibar Lattafa Perfumes</t>
@@ -472,7 +478,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Asad-Zanzibar-Lattafa-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Asad-Zanzibar-Lattafa-Perfumes/</t>
+    <t>https://perfamix.com/product/asad-zanzibar-lattafa-perfumes/</t>
   </si>
   <si>
     <t>Aventus Creed</t>
@@ -484,7 +490,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Aventus-Creed-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Aventus-Creed/</t>
+    <t>https://perfamix.com/product/aventus-creed/</t>
   </si>
   <si>
     <t>Baccarat Rouge 540</t>
@@ -496,7 +502,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Baccarat-Rouge-540-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Baccarat-Rouge-540/</t>
+    <t>https://perfamix.com/product/baccarat-rouge-540-maison/</t>
   </si>
   <si>
     <t>Baccarat Rouge 540 EDP</t>
@@ -508,7 +514,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Baccarat-Rouge-540-EDP-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Baccarat-Rouge-540-EDP/</t>
+    <t>https://perfamix.com/product/baccarat-rouge-540-extrait-de-parfum/</t>
   </si>
   <si>
     <t>Bad Boy Carolina Herrera</t>
@@ -517,7 +523,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Bad-Boy-Carolina-Herrera-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Bad-Boy-Carolina-Herrera/</t>
+    <t>https://perfamix.com/product/bad-boy-carolina-herrera/</t>
   </si>
   <si>
     <t>Badee Al Oud Amethyst</t>
@@ -529,7 +535,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Bade-Al-Oud-Amethyst-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Badee-Al-Oud-Amethyst/</t>
+    <t>https://perfamix.com/product/badee-al-oud-amethyst/</t>
   </si>
   <si>
     <t>Badee Al Oud Honor Glory</t>
@@ -541,7 +547,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Badee-Al-Oud-Honor-Glory-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Badee-Al-Oud-Honor-Glory/</t>
+    <t>https://perfamix.com/product/badee-al-oud-honor-glory/</t>
   </si>
   <si>
     <t>Badee Al Oud Oud for Glory</t>
@@ -553,7 +559,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Al-Oud-Oud-for-Glory-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Badee-Al-Oud-Oud-for-Glory/</t>
+    <t>https://perfamix.com/product/badee-al-oud-oud-for-glory/</t>
   </si>
   <si>
     <t>Badee Al Oud Sublime</t>
@@ -565,7 +571,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Badee-Al-Oud-Sublime-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Badee-Al-Oud-Sublime/</t>
+    <t>https://perfamix.com/product/badee-al-oud-sublime/</t>
   </si>
   <si>
     <t>Black Afgano</t>
@@ -577,7 +583,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Black-Afgano-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Black-Afgano/</t>
+    <t>https://perfamix.com/product/black-afgano/</t>
   </si>
   <si>
     <t>Black Opium</t>
@@ -589,7 +595,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Black-Opium-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Black-Opium/</t>
+    <t>https://perfamix.com/product/black-opium/</t>
   </si>
   <si>
     <t>Black Orchid</t>
@@ -601,7 +607,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Black-Orchid-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Black-Orchid/</t>
+    <t>https://perfamix.com/product/black-orchid/</t>
   </si>
   <si>
     <t>Black XS LExces</t>
@@ -613,7 +619,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Black-XS-LExces-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Black-XS-LExces/</t>
+    <t>https://perfamix.com/product/black-xs-lexces/</t>
   </si>
   <si>
     <t>Bleu de Chanel</t>
@@ -625,7 +631,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Bleu-de-Chanel-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Bleu-de-Chanel/</t>
+    <t>https://perfamix.com/product/bleu-de-chanel/</t>
   </si>
   <si>
     <t>Burberry Body Gold Limited Edition</t>
@@ -637,7 +643,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Burberry-Body-Gold-Limited-Edition-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Burberry-Body-Gold-Limited-Edition/</t>
+    <t>https://perfamix.com/product/burberry-body-gold-limited-edition/</t>
   </si>
   <si>
     <t>Bombshell New York</t>
@@ -649,7 +655,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Bombshell-New-York-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Bombshell-New-York/</t>
+    <t>https://perfamix.com/product/bombshell-new-york/</t>
   </si>
   <si>
     <t>Bright Crystal</t>
@@ -662,7 +668,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Bright-Crystal-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Bright-Crystal/</t>
+    <t>https://perfamix.com/product/bright-crystal/</t>
   </si>
   <si>
     <t>Bvlgari Man In Black</t>
@@ -674,7 +680,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Bvlgari-Man-In-Black-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Bvlgari-Man-In-Black/</t>
+    <t>https://perfamix.com/product/bvlgari-man-in-black/</t>
   </si>
   <si>
     <t>Club de Nuit Intense Man</t>
@@ -686,7 +692,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Club-de-Nuit-Intense-Man-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Club-de-Nuit-Intense-Man/</t>
+    <t>https://perfamix.com/product/club-de-nuit-intense-man/</t>
   </si>
   <si>
     <t>Coco Mademoiselle</t>
@@ -698,7 +704,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Coco-Mademoiselle-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Coco-Mademoiselle/</t>
+    <t>https://perfamix.com/product/coco-mademoiselle/</t>
   </si>
   <si>
     <t>Delina</t>
@@ -710,7 +716,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Delina-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Delina/</t>
+    <t>https://perfamix.com/product/delina/</t>
   </si>
   <si>
     <t>Devotion</t>
@@ -722,7 +728,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Devotion-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Devotion/</t>
+    <t>https://perfamix.com/product/devotion/</t>
   </si>
   <si>
     <t>Dior Homme Intense</t>
@@ -734,7 +740,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Dior-Homme-Intense-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Dior-Homme-Intense/</t>
+    <t>https://perfamix.com/product/dior-homme-intense/</t>
   </si>
   <si>
     <t>Lacoste L.12.12. Noir</t>
@@ -746,7 +752,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Lacoste-L-12-12-Noir-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Lacoste-L.12.12.-Noir/</t>
+    <t>https://perfamix.com/product/lacoste-l-12-12-noir/</t>
   </si>
   <si>
     <t>Eros Flame</t>
@@ -758,7 +764,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Eros-Flame-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Eros-Flame/</t>
+    <t>https://perfamix.com/product/eros-flame/</t>
   </si>
   <si>
     <t>Eros</t>
@@ -770,7 +776,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Eros-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Eros/</t>
+    <t>https://perfamix.com/product/eros/</t>
   </si>
   <si>
     <t>Fahrenheit</t>
@@ -782,7 +788,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Fahrenheit-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Fahrenheit/</t>
+    <t>https://perfamix.com/product/fahrenheit/</t>
   </si>
   <si>
     <t>Gaultier Divine</t>
@@ -794,7 +800,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Gaultier-Divine-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Gaultier-Divine/</t>
+    <t>https://perfamix.com/product/gaultier-divine/</t>
   </si>
   <si>
     <t>Gentleman Society</t>
@@ -806,7 +812,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Gentleman-Society-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Gentleman-Society/</t>
+    <t>https://perfamix.com/product/gentleman-society/</t>
   </si>
   <si>
     <t>Girl of Now</t>
@@ -818,7 +824,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Girl-of-Now-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Girl-of-Now/</t>
+    <t>https://perfamix.com/product/girl-of-now/</t>
   </si>
   <si>
     <t>Good Girl Blush</t>
@@ -830,7 +836,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Good-Girl-Blush-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Good-Girl-Blush/</t>
+    <t>https://perfamix.com/product/good-girl-blush/</t>
   </si>
   <si>
     <t>Good Girl Glorious Gold Collector Edition</t>
@@ -842,7 +848,10 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Good-Girl-GGCE-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Good-Girl-Glorious-Gold-Collector-Edition/</t>
+    <t>https://perfamix.com/product/good-girl-glorious-gold-collector-edition/</t>
+  </si>
+  <si>
+    <t>Good Girl Supreme</t>
   </si>
   <si>
     <t>Good Girl Suprême is a rich oriental-floral fragrance for women, blending juicy forest fruits and Egyptian jasmine with tonka bean and tuberose. Vetiver creates an earthy, woody finish that balances the fragrance’s sweet and sensual character.</t>
@@ -851,6 +860,9 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Good-Girl-Supreme-1.jpg</t>
   </si>
   <si>
+    <t>https://perfamix.com/product/good-girl-supreme/</t>
+  </si>
+  <si>
     <t>Gucci Bloom Ambrosia di Fiori</t>
   </si>
   <si>
@@ -860,7 +872,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Gucci-Bloom-Ambrosia-di-Fiori-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Gucci-Bloom-Ambrosia-di-Fiori/</t>
+    <t>https://perfamix.com/product/gucci-bloom-ambrosia-di-fiori/</t>
   </si>
   <si>
     <t>Herod</t>
@@ -872,7 +884,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Herod-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Herod/</t>
+    <t>https://perfamix.com/product/herod/</t>
   </si>
   <si>
     <t>Idole</t>
@@ -884,7 +896,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Idole-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Idole/</t>
+    <t>https://perfamix.com/product/idole/</t>
   </si>
   <si>
     <t>Invictus Legend</t>
@@ -896,7 +908,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Invictus-Legend-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Invictus-Legend/</t>
+    <t>https://perfamix.com/product/invictus-legend/</t>
   </si>
   <si>
     <t>Invictus</t>
@@ -908,7 +920,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Invictus-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Invictus/</t>
+    <t>https://perfamix.com/product/invictus/</t>
   </si>
   <si>
     <t>Invictus Victory</t>
@@ -920,7 +932,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Invictus-Victory-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Invictus-Victory/</t>
+    <t>https://perfamix.com/product/invictus-victory/</t>
   </si>
   <si>
     <t>Jadore</t>
@@ -932,7 +944,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Jadore-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Jadore/</t>
+    <t>https://perfamix.com/product/jadore/</t>
   </si>
   <si>
     <t>Ultra Male</t>
@@ -944,7 +956,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Ultra-Male-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Ultra-Male/</t>
+    <t>https://perfamix.com/product/ultra-male/</t>
   </si>
   <si>
     <t>Le Male Elixir</t>
@@ -956,7 +968,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Le-Male-Elixir-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Le-Male-Elixir/</t>
+    <t>https://perfamix.com/product/le-male-elixir/</t>
   </si>
   <si>
     <t>Kalan</t>
@@ -968,7 +980,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Kalan-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Kalan/</t>
+    <t>https://perfamix.com/product/kalan/</t>
   </si>
   <si>
     <t>Layton</t>
@@ -980,7 +992,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Layton-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Layton/</t>
+    <t>https://perfamix.com/product/layton/</t>
   </si>
   <si>
     <t>Khamrah</t>
@@ -992,7 +1004,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Khamrah-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Khamrah/</t>
+    <t>https://perfamix.com/product/khamrah/</t>
   </si>
   <si>
     <t>Le Parfum</t>
@@ -1004,7 +1016,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Le-Parfum-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Le-Parfum/</t>
+    <t>https://perfamix.com/product/le-parfum/</t>
   </si>
   <si>
     <t>Libre</t>
@@ -1016,7 +1028,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Libre-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Libre/</t>
+    <t>https://perfamix.com/product/libre/</t>
   </si>
   <si>
     <t>Lost Cherry</t>
@@ -1028,7 +1040,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Lost-Cherry-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Lost-Cherry/</t>
+    <t>https://perfamix.com/product/lost-cherry/</t>
   </si>
   <si>
     <t>My Way</t>
@@ -1040,7 +1052,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/My-Way-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/My-Way/</t>
+    <t>https://perfamix.com/product/my-way/</t>
   </si>
   <si>
     <t>Narciso Poudree</t>
@@ -1052,7 +1064,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Narciso-Rodriguez-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Narciso-Poudree/</t>
+    <t>https://perfamix.com/product/narciso-poudree/</t>
   </si>
   <si>
     <t>Fleur Musc</t>
@@ -1064,7 +1076,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Fleur-Musc-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Fleur-Musc/</t>
+    <t>https://perfamix.com/product/fleur-musc/</t>
   </si>
   <si>
     <t>Noir Extreme</t>
@@ -1076,7 +1088,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Noir-Extreme-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Noir-Extreme/</t>
+    <t>https://perfamix.com/product/noir-extreme/</t>
   </si>
   <si>
     <t>Olympea</t>
@@ -1088,7 +1100,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Olympea-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Olympea/</t>
+    <t>https://perfamix.com/product/olympea/</t>
   </si>
   <si>
     <t>Ombre Leather</t>
@@ -1100,7 +1112,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Ombre-Leather-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Ombre-Leather/</t>
+    <t>https://perfamix.com/product/ombre-leather/</t>
   </si>
   <si>
     <t>Oriana</t>
@@ -1112,7 +1124,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Oriana-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Oriana/</t>
+    <t>https://perfamix.com/product/oriana/</t>
   </si>
   <si>
     <t>Oud Minerale</t>
@@ -1124,7 +1136,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Oud-Minerale-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Oud-Minerale/</t>
+    <t>https://perfamix.com/product/oud-minerale/</t>
   </si>
   <si>
     <t>Oud Wood is a refined oriental-woody fragrance for women and men, blending rich oud and Brazilian rosewood with cardamom and Sichuan pepper. Sandalwood, vetiver, vanilla, tonka bean and amber create a warm, smooth and sophisticated finish.</t>
@@ -1133,6 +1145,9 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Oud-Wood-1-scaled.jpg</t>
   </si>
   <si>
+    <t>https://perfamix.com/product/tom-ford-oud-wood/</t>
+  </si>
+  <si>
     <t>Pegasus</t>
   </si>
   <si>
@@ -1142,7 +1157,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Pegasus-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Pegasus/</t>
+    <t>https://perfamix.com/product/pegasus/</t>
   </si>
   <si>
     <t>Prada Paradoxe</t>
@@ -1154,7 +1169,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Prada-Paradoxe-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Prada-Paradoxe/</t>
+    <t>https://perfamix.com/product/prada-paradoxe/</t>
   </si>
   <si>
     <t>Pure XS</t>
@@ -1166,7 +1181,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Pure-XS-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Pure-XS/</t>
+    <t>https://perfamix.com/product/pure-xs/</t>
   </si>
   <si>
     <t>Red Tobacco</t>
@@ -1178,7 +1193,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Red-Tobacco-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Red-Tobacco/</t>
+    <t>https://perfamix.com/product/red-tobacco/</t>
   </si>
   <si>
     <t>Roses Vanille</t>
@@ -1190,7 +1205,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Roses-Vanille-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Roses-Vanille/</t>
+    <t>https://perfamix.com/product/roses-vanille/</t>
   </si>
   <si>
     <t>Sauvage</t>
@@ -1202,7 +1217,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Sauvage-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Sauvage/</t>
+    <t>https://perfamix.com/product/sauvage/</t>
   </si>
   <si>
     <t>Sauvage Elixir</t>
@@ -1214,7 +1229,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Sauvage-Elixir-2-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Sauvage-Elixir/</t>
+    <t>https://perfamix.com/product/sauvage-elixir/</t>
   </si>
   <si>
     <t>Scandal A Paris</t>
@@ -1226,7 +1241,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Scandal-A-Paris-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Scandal-A-Paris/</t>
+    <t>https://perfamix.com/product/scandal-a-paris/</t>
   </si>
   <si>
     <t>Scandal Pour Homme</t>
@@ -1238,7 +1253,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Scandal-Pour-Homme-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Scandal-Pour-Homme/</t>
+    <t>https://perfamix.com/product/scandal-pour-homme/</t>
   </si>
   <si>
     <t>Sense</t>
@@ -1250,7 +1265,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Sense-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Sense/</t>
+    <t>https://perfamix.com/product/sense/</t>
   </si>
   <si>
     <t>Spicebomb Infrared</t>
@@ -1262,7 +1277,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Spicebomb-Infrared-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Spicebomb-Infrared/</t>
+    <t>https://perfamix.com/product/spicebomb-infrared/</t>
   </si>
   <si>
     <t>Spicebomb Night Vision</t>
@@ -1274,7 +1289,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Spicebomb-Night-Vision-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Spicebomb-Night-Vision/</t>
+    <t>https://perfamix.com/product/spicebomb-night-vision/</t>
   </si>
   <si>
     <t>Stronger With You Absolutely</t>
@@ -1286,7 +1301,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Stronger-With-You-Absolutely-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Stronger-With-You-Absolutely/</t>
+    <t>https://perfamix.com/product/stronger-with-you-absolutely/</t>
   </si>
   <si>
     <t>Stronger With You Amber</t>
@@ -1298,7 +1313,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Stronger-With-You-Amber-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Stronger-With-You-Amber/</t>
+    <t>https://perfamix.com/product/stronger-with-you-amber/</t>
   </si>
   <si>
     <t>Stronger With You Oud</t>
@@ -1310,7 +1325,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Stronger-With-You-Oud-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Stronger-With-You-Oud/</t>
+    <t>https://perfamix.com/product/stronger-with-you-oud/</t>
   </si>
   <si>
     <t>Stronger With You Tobacco</t>
@@ -1322,7 +1337,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Stronger-With-You-Tobacco-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Stronger-With-You-Tobacco/</t>
+    <t>https://perfamix.com/product/stronger-with-you-tobacco/</t>
   </si>
   <si>
     <t>The One for Men</t>
@@ -1334,7 +1349,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/The-One-for-Men-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/The-One-for-Men/</t>
+    <t>https://perfamix.com/product/the-one-for-men/</t>
   </si>
   <si>
     <t>Tresor Midnight Rose</t>
@@ -1346,7 +1361,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Tresor-Midnight-Rose-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Tresor-Midnight-Rose/</t>
+    <t>https://perfamix.com/product/tresor-midnight-rose/</t>
   </si>
   <si>
     <t>Donna Born In Roma Intense</t>
@@ -1358,7 +1373,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Born-In-Roma-Intense-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Donna-Born-In-Roma-Intense/</t>
+    <t>https://perfamix.com/product/donna-born-in-roma-intense/</t>
   </si>
   <si>
     <t>Pour Homme Dylan Blue</t>
@@ -1370,7 +1385,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Pour-Homme-Dylan-Blue-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Pour-Homme-Dylan-Blue/</t>
+    <t>https://perfamix.com/product/pour-homme-dylan-blue/</t>
   </si>
   <si>
     <t>Very Good Girl</t>
@@ -1382,7 +1397,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Very-Good-Girl-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Very-Good-Girl/</t>
+    <t>https://perfamix.com/product/very-good-girl/</t>
   </si>
   <si>
     <t>Wanted by Night</t>
@@ -1394,7 +1409,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Wanted-by-Night-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Wanted-by-Night/</t>
+    <t>https://perfamix.com/product/wanted-by-night/</t>
   </si>
   <si>
     <t>XJ 1861 Naxos</t>
@@ -1406,7 +1421,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/XJ-1861-Naxos-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/XJ-1861-Naxos/</t>
+    <t>https://perfamix.com/product/xj-1861-naxos/</t>
   </si>
   <si>
     <t>Y Eau de Parfum</t>
@@ -1418,7 +1433,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Y-Eau-de-Parfum-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Y-Eau-de-Parfum/</t>
+    <t>https://perfamix.com/product/y-eau-de-parfum/</t>
   </si>
   <si>
     <t>Y Le Parfum</t>
@@ -1430,7 +1445,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Y-Le-Parfum-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Y-Le-Parfum/</t>
+    <t>https://perfamix.com/product/y-le-parfum/</t>
   </si>
   <si>
     <t>Yara Candy</t>
@@ -1442,7 +1457,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Yara-Candy-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Yara-Candy/</t>
+    <t>https://perfamix.com/product/yara-candy/</t>
   </si>
   <si>
     <t>Yara</t>
@@ -1454,7 +1469,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/08/Yara-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Yara/</t>
+    <t>https://perfamix.com/product/yara/</t>
   </si>
   <si>
     <t>Stronger With You Freeze</t>
@@ -1466,7 +1481,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Stronger-With-You-Freeze-1-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Stronger-With-You-Freeze/</t>
+    <t>https://perfamix.com/product/emporio-armani-stronger-with-you-freeze/</t>
   </si>
   <si>
     <t>1 Million Elixir</t>
@@ -1478,7 +1493,31 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/One-Million-Elixir-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/1-Million-Elixir/</t>
+    <t>https://perfamix.com/product/1-million-elixir/</t>
+  </si>
+  <si>
+    <t>Intense Icons</t>
+  </si>
+  <si>
+    <t>The Intense Icons Bundle combines Ultra Male, Stronger With You Intensely, Spicebomb Extreme and Sauvage Elixir in one powerful masculine collection. Expect sweet vanilla, warm spices, tobacco, aromatic lavender, rich woods and deep amber notes — ideal for evenings, dates and cooler weather.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/09/Product-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/Intense-Icons/</t>
+  </si>
+  <si>
+    <t>Velvet Vice</t>
+  </si>
+  <si>
+    <t>Velvet Vice combines Dior Homme Intense, Stronger With You Intensely and Black Orchid in one rich, sophisticated selection. Powdery iris, warm toffee, vanilla, dark florals, spices and woods create an addictive scent wardrobe designed for evenings, dates and cooler weather.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/09/Velvet-Vice-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/Velvet-Vice/</t>
   </si>
   <si>
     <t>Le Male Le Parfum</t>
@@ -1490,7 +1529,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Le-Male-Le-Parfum-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Le-Male-Le-Parfum/</t>
+    <t>https://perfamix.com/product/le-male-le-parfum/</t>
   </si>
   <si>
     <t>Invictus Aqua</t>
@@ -1502,7 +1541,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Invictus-Aqua-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Invictus-Aqua/</t>
+    <t>https://perfamix.com/product/invictus-aqua/</t>
   </si>
   <si>
     <t>Silver Scent</t>
@@ -1514,7 +1553,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Silver-Scent-Jacques-Bogart-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Silver-Scent/</t>
+    <t>https://perfamix.com/product/silver-scent/</t>
   </si>
   <si>
     <t>Stronger With You Leather</t>
@@ -1526,7 +1565,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Stronger-With-You-Leather-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Stronger-With-You-Leather/</t>
+    <t>https://perfamix.com/product/stronger-with-you-leather/</t>
   </si>
   <si>
     <t>Stronger With You Intensely</t>
@@ -1538,7 +1577,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Stronger-With-You-Intensely-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Stronger-With-You-Intensely/</t>
+    <t>https://perfamix.com/product/stronger-with-you-intensely/</t>
   </si>
   <si>
     <t>Stronger With You Sandalwood</t>
@@ -1550,7 +1589,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Stronger-With-You-Sandalwood-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Stronger-With-You-Sandalwood/</t>
+    <t>https://perfamix.com/product/stronger-with-you-sandalwood/</t>
   </si>
   <si>
     <t>Burberry Her</t>
@@ -1562,7 +1601,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Burberry-Her-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Burberry-Her/</t>
+    <t>https://perfamix.com/product/burberry-her/</t>
   </si>
   <si>
     <t>Scandal By Night</t>
@@ -1574,7 +1613,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Scandal-By-Night-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Scandal-By-Night/</t>
+    <t>https://perfamix.com/product/scandal-by-night/</t>
   </si>
   <si>
     <t>Le Beau Paradise Garden</t>
@@ -1586,7 +1625,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Le-Beau-Paradise-Garden-Jean-Paul-Gaultier-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Le-Beau-Paradise-Garden/</t>
+    <t>https://perfamix.com/product/le-beau-paradise-garden/</t>
   </si>
   <si>
     <t>Imagination</t>
@@ -1598,7 +1637,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Imagination-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Imagination/</t>
+    <t>https://perfamix.com/product/imagination/</t>
   </si>
   <si>
     <t>Pacific Chill</t>
@@ -1610,7 +1649,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Pacific-Chill-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Pacific-Chill/</t>
+    <t>https://perfamix.com/product/pacific-chill/</t>
   </si>
   <si>
     <t>Symphony</t>
@@ -1622,7 +1661,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Symphony-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Symphony/</t>
+    <t>https://perfamix.com/product/symphony/</t>
   </si>
   <si>
     <t>God of Fire</t>
@@ -1634,7 +1673,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/God-Of-Fire-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/God-of-Fire/</t>
+    <t>https://perfamix.com/product/god-of-fire/</t>
   </si>
   <si>
     <t>Megamare</t>
@@ -1646,7 +1685,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Megamare-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Megamare/</t>
+    <t>https://perfamix.com/product/megamare/</t>
   </si>
   <si>
     <t>1 Million Golden Oud</t>
@@ -1658,7 +1697,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/One-Million-Golden-Oud-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/1-Million-Golden-Oud/</t>
+    <t>https://perfamix.com/product/1-million-golden-oud/</t>
   </si>
   <si>
     <t>212 VIP Men</t>
@@ -1670,7 +1709,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/212-VIP-MEN-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/212-VIP-Men/</t>
+    <t>https://perfamix.com/product/212-vip-men/</t>
   </si>
   <si>
     <t>212 Men NYC</t>
@@ -1682,7 +1721,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/212-NYC-MEN-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/212-Men-NYC/</t>
+    <t>https://perfamix.com/product/212-men-nyc/</t>
   </si>
   <si>
     <t>Phantom Parfum</t>
@@ -1694,7 +1733,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Phantom-Parfum-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Phantom-Parfum/</t>
+    <t>https://perfamix.com/product/phantom-parfum/</t>
   </si>
   <si>
     <t>Silver Mountain Water</t>
@@ -1706,7 +1745,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Silver-Mountain-Water-1-1-scaled.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Silver-Mountain-Water/</t>
+    <t>https://perfamix.com/product/silver-mountain-water/</t>
   </si>
   <si>
     <t>Bleu de Chanel LExclusif</t>
@@ -1718,7 +1757,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/bleu-de-chanel-l-exclusif-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Bleu-de-Chanel-LExclusif/</t>
+    <t>https://perfamix.com/product/bleu-de-chanel-lexclusif/</t>
   </si>
   <si>
     <t>Very Sexy Now</t>
@@ -1730,7 +1769,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Very-Sexy-Now-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Very-Sexy-Now/</t>
+    <t>https://perfamix.com/product/very-sexy-now/</t>
   </si>
   <si>
     <t>Le Beau Le Parfum</t>
@@ -1742,7 +1781,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Le-Beau-Jean-Paul-Gaultier-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Le-Beau-Le-Parfum/</t>
+    <t>https://perfamix.com/product/le-beau-le-parfum/</t>
   </si>
   <si>
     <t>Vanilla Sex</t>
@@ -1754,7 +1793,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Vanilla-Sex-Tom-Ford-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Vanilla-Sex/</t>
+    <t>https://perfamix.com/product/vanilla-sex/</t>
   </si>
   <si>
     <t>Costa Azzurra</t>
@@ -1766,7 +1805,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Costa-Azzurra-Tom-Ford-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Costa-Azzurra/</t>
+    <t>https://perfamix.com/product/costa-azzurra/</t>
   </si>
   <si>
     <t>Erba Pura</t>
@@ -1778,7 +1817,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Erba-Pura-Xerjoff-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Erba-Pura/</t>
+    <t>https://perfamix.com/product/erba-pura/</t>
   </si>
   <si>
     <t>Oud Ispahan</t>
@@ -1790,7 +1829,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Oud-Ispahan-Dior-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Oud-Ispahan/</t>
+    <t>https://perfamix.com/product/oud-ispahan/</t>
   </si>
   <si>
     <t>Imperial Valley</t>
@@ -1802,7 +1841,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Imperial-Valley-Gissah-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Imperial-Valley/</t>
+    <t>https://perfamix.com/product/imperial-valley/</t>
   </si>
   <si>
     <t>One Only</t>
@@ -1814,7 +1853,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/One-Only-Gissah-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/One-Only/</t>
+    <t>https://perfamix.com/product/one-only/</t>
   </si>
   <si>
     <t>Bitter Peach</t>
@@ -1826,7 +1865,7 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Bitter-Peach-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Bitter-Peach/</t>
+    <t>https://perfamix.com/product/bitter-peach/</t>
   </si>
   <si>
     <t>Olympea Legend</t>
@@ -1838,19 +1877,235 @@
     <t>https://perfamix.com/wp-content/uploads/2026/09/Olympea-Legend-1.jpg</t>
   </si>
   <si>
-    <t>https://perfamix.com/product/Olympea-Legend/</t>
-  </si>
-  <si>
-    <t>Althair Parfums de Marly</t>
-  </si>
-  <si>
-    <t>Good Girl Supreme</t>
-  </si>
-  <si>
-    <t>https://perfamix.com/product/Good-Girl-Supreme/</t>
-  </si>
-  <si>
-    <t>https://perfamix.com/product/Althair-Parfums-de-Marly/</t>
+    <t>https://perfamix.com/product/olympea-legend/</t>
+  </si>
+  <si>
+    <t>Armani Code Parfum</t>
+  </si>
+  <si>
+    <t>Armani Code Parfum is a woody-aromatic fragrance for men, blending fresh bergamot and bergamot leaf with elegant iris, clary sage and orris. Tonka bean and cedar create a warm, smooth and sophisticated masculine finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/ARMANI-CODE-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/armani-code-parfum/</t>
+  </si>
+  <si>
+    <t>Bianco Latte</t>
+  </si>
+  <si>
+    <t>Bianco Latte is a sweet oriental-vanilla fragrance for women and men, blending creamy caramel with warm honey and coumarin. Vanilla and white musk create a smooth, cozy and addictive gourmand finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/Bianco-Latte-Giardini-Di-Toscana-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/bianco-latte/</t>
+  </si>
+  <si>
+    <t>Divine Decadence</t>
+  </si>
+  <si>
+    <t>Divine Decadence is an oriental-floral fragrance for women, blending sparkling champagne, orange blossom and bergamot with honeysuckle, hortensia and gardenia. Vanilla, saffron and amber create a warm, sweet and sophisticated feminine finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/Divine-Decadence-Marc-Jacobs-for-women-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/divine-decadence/</t>
+  </si>
+  <si>
+    <t>Eau de Lacoste L.12.12. White</t>
+  </si>
+  <si>
+    <t>Eau de Lacoste L.12.12. White is a fresh woody-aromatic fragrance for men, blending grapefruit, rosemary and cardamom with ylang-ylang and tuberose. Cedar, suede, vetiver and leather create a clean, dry and refined masculine finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/LACOSTE-WHITE-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/eau-de-lacoste-l-12-12-white/</t>
+  </si>
+  <si>
+    <t>Eclaire</t>
+  </si>
+  <si>
+    <t>Eclaire is a sweet floral-fruity gourmand fragrance for women, blending caramel, milk and sugar with honey and white flowers. Vanilla, praline and musk create a creamy, warm and comforting finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/Eclaire-Lattafa-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/eclaire/</t>
+  </si>
+  <si>
+    <t>Eilish</t>
+  </si>
+  <si>
+    <t>Eilish is a warm oriental-vanilla fragrance for women, blending sugar, red berries and mandarin orange with creamy vanilla, cacao, spicy notes and rose. Tonka bean, amber, musk and woody notes create a sweet, smooth and sensual finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/Eilish-Billie-Eilish-for-women-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/eilish/</t>
+  </si>
+  <si>
+    <t>Epic Woman</t>
+  </si>
+  <si>
+    <t>Epic Woman is a rich oriental-floral fragrance for women, combining warm cinnamon and aromatic spices with elegant Damask rose, tea and jasmine. Oud, olibanum, amber, woods, vanilla and musk create a deep, warm and sophisticated finish with a mysterious feminine character.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/AMOUAGE-EPIC-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/epic-woman/</t>
+  </si>
+  <si>
+    <t>Explorer</t>
+  </si>
+  <si>
+    <t>Explorer is a woody-aromatic fragrance for men, blending fresh bergamot, pink pepper and clary sage with Haitian vetiver and leather. Ambroxan, Akigalawood, patchouli and cacao create a modern, woody and masculine finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/Montblanc-explorer-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/explorer/</t>
+  </si>
+  <si>
+    <t>Hersh Lahab</t>
+  </si>
+  <si>
+    <t>Hersh Lahab is an aromatic fragrance for women and men, blending black pepper, vetiver and basil with Timur pepper and grapefruit. Patchouli creates an earthy, woody and powerful finish with a bold modern character.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/Hersh-Lahab-Perfume-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/hersh-lahab/</t>
+  </si>
+  <si>
+    <t>Interlude Man</t>
+  </si>
+  <si>
+    <t>Interlude Man is a deep oriental-woody fragrance for men, blending spicy oregano, pepper and bergamot with smoky incense, amber and warm resins. Oud, leather, sandalwood and patchouli create a rich, powerful and sophisticated masculine finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/AMOUAGE-INTERLUDE-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/interlude-man/</t>
+  </si>
+  <si>
+    <t>K by Dolce &amp; Gabbana</t>
+  </si>
+  <si>
+    <t>K by Dolce &amp; Gabbana is a fresh woody-aromatic fragrance for men, blending juniper berries, citrus, blood orange and Sicilian lemon with pimento, lavender and clary sage. Vetiver, cedar and patchouli create a clean, woody and masculine finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/Dolce-Gabanna-King-EDT-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/k-by-dolce-gabbana/</t>
+  </si>
+  <si>
+    <t>K by Dolce &amp; Gabbana Eau de Parfum</t>
+  </si>
+  <si>
+    <t>K by Dolce &amp; Gabbana Eau de Parfum is a woody-spicy fragrance for men, blending blood orange, juniper berries and cardamom with fig nectar, lavender and aromatic herbs. Cedar, patchouli, vetiver and cypriol create a warm, woody and masculine finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/Dolce-Gabbanna-King-EDP-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/k-by-dolce-gabbana-eau-de-parfum/</t>
+  </si>
+  <si>
+    <t>L’Eau d’Issey Pour Homme</t>
+  </si>
+  <si>
+    <t>L’Eau d’Issey Pour Homme is a fresh woody-aquatic fragrance for men, blending bright yuzu, lemon and bergamot with aromatic herbs, blue lotus and warm spices. Vetiver, cedar, sandalwood, musk, amber and tobacco create a clean, woody and refined masculine finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/issey-miyake-leau-dissey-pour-homme-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/leau-dissey-pour-homme/</t>
+  </si>
+  <si>
+    <t>Mon Guerlain</t>
+  </si>
+  <si>
+    <t>Mon Guerlain is a warm oriental-woody fragrance for women, blending aromatic lavender and bergamot with iris, jasmine sambac and rose. Tahitian vanilla, sandalwood, benzoin and patchouli create a smooth, sweet and elegant feminine finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/MON-GURELIAN-EDP-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/mon-guerlain/</t>
+  </si>
+  <si>
+    <t>Musamam</t>
+  </si>
+  <si>
+    <t>Musamam is a woody-aromatic fragrance for women and men, blending saffron, Italian mandarin and lavender with amberwood, Virginia cedar and geranium. Akigalawood, incense and labdanum create a smoky, warm and resinous finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/MUSAMAM-EDP-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/musamam/</t>
+  </si>
+  <si>
+    <t>Spicebomb Extreme</t>
+  </si>
+  <si>
+    <t>Spicebomb Extreme is a bold oriental-spicy fragrance for men, combining warm cinnamon, saffron and cumin with rich tobacco, bourbon whiskey and creamy vanilla. The result is a deep, sweet and intensely masculine scent perfect for evenings and cooler weather.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/Spicebomb-Extreme-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/spicebomb-extreme/</t>
+  </si>
+  <si>
+    <t>Sì Passione</t>
+  </si>
+  <si>
+    <t>Sì Passione is a floral-fruity fragrance for women, blending juicy pear, black currant and pink pepper with pineapple, rose and jasmine. Vanilla, cedar, patchouli and amberwood create a warm, smooth and sensual feminine finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/Si-Passione-Red-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/si-passione/</t>
+  </si>
+  <si>
+    <t>Tobacco Vanille</t>
+  </si>
+  <si>
+    <t>Tobacco Vanille is a rich oriental-spicy fragrance for women and men, blending tobacco leaf and warm spices with creamy vanilla, cacao and tonka bean. Dried fruits and woody notes create a deep, sweet and luxurious finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/TOM-FORD-TOBACCO-VANILLA-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/tobacco-vanille/</t>
+  </si>
+  <si>
+    <t>Vanilla 28</t>
+  </si>
+  <si>
+    <t>Vanilla 28 is a warm oriental-vanilla fragrance for women and men, blending vanilla orchid and jasmine with brown sugar and tonka bean. Amber, amberwood, musk and patchouli create a smooth, sweet and sensual finish.</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/wp-content/uploads/2026/10/kayali-vanilla-28-1.jpg</t>
+  </si>
+  <si>
+    <t>https://perfamix.com/product/vanilla-28/</t>
   </si>
 </sst>
 </file>
@@ -2252,7 +2507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
@@ -2982,10 +3237,10 @@
         <v>14347</v>
       </c>
       <c r="B32" t="s">
-        <v>605</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
@@ -2994,10 +3249,10 @@
         <v>10</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>608</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -3005,10 +3260,10 @@
         <v>14359</v>
       </c>
       <c r="B33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D33" t="s">
         <v>97</v>
@@ -3017,10 +3272,10 @@
         <v>15</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -3028,10 +3283,10 @@
         <v>14366</v>
       </c>
       <c r="B34" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
@@ -3040,10 +3295,10 @@
         <v>15</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G34" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -3051,10 +3306,10 @@
         <v>14376</v>
       </c>
       <c r="B35" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -3063,10 +3318,10 @@
         <v>15</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G35" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -3074,10 +3329,10 @@
         <v>14390</v>
       </c>
       <c r="B36" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D36" t="s">
         <v>97</v>
@@ -3086,10 +3341,10 @@
         <v>15</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G36" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -3097,10 +3352,10 @@
         <v>14402</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -3109,10 +3364,10 @@
         <v>10</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G37" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -3120,10 +3375,10 @@
         <v>14411</v>
       </c>
       <c r="B38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -3132,10 +3387,10 @@
         <v>32</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -3143,10 +3398,10 @@
         <v>14422</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C39" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
@@ -3155,10 +3410,10 @@
         <v>32</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G39" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -3166,10 +3421,10 @@
         <v>14431</v>
       </c>
       <c r="B40" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C40" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
@@ -3178,10 +3433,10 @@
         <v>10</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G40" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -3189,10 +3444,10 @@
         <v>14441</v>
       </c>
       <c r="B41" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C41" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D41" t="s">
         <v>97</v>
@@ -3201,10 +3456,10 @@
         <v>32</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G41" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -3212,10 +3467,10 @@
         <v>14449</v>
       </c>
       <c r="B42" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C42" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D42" t="s">
         <v>97</v>
@@ -3224,10 +3479,10 @@
         <v>32</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -3235,10 +3490,10 @@
         <v>14460</v>
       </c>
       <c r="B43" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C43" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D43" t="s">
         <v>97</v>
@@ -3247,10 +3502,10 @@
         <v>32</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G43" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -3258,10 +3513,10 @@
         <v>14469</v>
       </c>
       <c r="B44" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C44" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D44" t="s">
         <v>97</v>
@@ -3270,10 +3525,10 @@
         <v>32</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G44" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -3281,10 +3536,10 @@
         <v>14478</v>
       </c>
       <c r="B45" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C45" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D45" t="s">
         <v>9</v>
@@ -3293,10 +3548,10 @@
         <v>32</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G45" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -3304,10 +3559,10 @@
         <v>14496</v>
       </c>
       <c r="B46" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C46" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D46" t="s">
         <v>9</v>
@@ -3316,10 +3571,10 @@
         <v>15</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G46" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -3327,10 +3582,10 @@
         <v>14506</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C47" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D47" t="s">
         <v>9</v>
@@ -3339,10 +3594,10 @@
         <v>32</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G47" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -3350,10 +3605,10 @@
         <v>14522</v>
       </c>
       <c r="B48" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C48" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D48" t="s">
         <v>9</v>
@@ -3362,10 +3617,10 @@
         <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G48" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -3373,10 +3628,10 @@
         <v>14530</v>
       </c>
       <c r="B49" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C49" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D49" t="s">
         <v>9</v>
@@ -3385,10 +3640,10 @@
         <v>10</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G49" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -3396,10 +3651,10 @@
         <v>14543</v>
       </c>
       <c r="B50" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D50" t="s">
         <v>9</v>
@@ -3408,10 +3663,10 @@
         <v>15</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G50" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -3419,10 +3674,10 @@
         <v>14551</v>
       </c>
       <c r="B51" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C51" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D51" t="s">
         <v>97</v>
@@ -3431,10 +3686,10 @@
         <v>15</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G51" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
@@ -3442,10 +3697,10 @@
         <v>14607</v>
       </c>
       <c r="B52" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D52" t="s">
         <v>9</v>
@@ -3454,10 +3709,10 @@
         <v>15</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G52" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3465,10 +3720,10 @@
         <v>14618</v>
       </c>
       <c r="B53" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C53" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D53" t="s">
         <v>9</v>
@@ -3477,10 +3732,10 @@
         <v>10</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G53" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -3488,10 +3743,10 @@
         <v>14630</v>
       </c>
       <c r="B54" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C54" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D54" t="s">
         <v>97</v>
@@ -3500,10 +3755,10 @@
         <v>10</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G54" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -3511,10 +3766,10 @@
         <v>14640</v>
       </c>
       <c r="B55" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C55" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D55" t="s">
         <v>9</v>
@@ -3523,10 +3778,10 @@
         <v>15</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G55" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3534,10 +3789,10 @@
         <v>14651</v>
       </c>
       <c r="B56" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C56" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D56" t="s">
         <v>9</v>
@@ -3546,10 +3801,10 @@
         <v>15</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G56" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3557,10 +3812,10 @@
         <v>14661</v>
       </c>
       <c r="B57" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C57" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D57" t="s">
         <v>9</v>
@@ -3569,10 +3824,10 @@
         <v>15</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G57" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3580,10 +3835,10 @@
         <v>14670</v>
       </c>
       <c r="B58" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C58" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D58" t="s">
         <v>9</v>
@@ -3592,10 +3847,10 @@
         <v>10</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G58" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3603,10 +3858,10 @@
         <v>14679</v>
       </c>
       <c r="B59" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C59" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D59" t="s">
         <v>97</v>
@@ -3615,10 +3870,10 @@
         <v>10</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3626,10 +3881,10 @@
         <v>14692</v>
       </c>
       <c r="B60" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C60" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
@@ -3638,10 +3893,10 @@
         <v>10</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G60" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3649,10 +3904,10 @@
         <v>14701</v>
       </c>
       <c r="B61" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C61" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D61" t="s">
         <v>9</v>
@@ -3661,10 +3916,10 @@
         <v>10</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G61" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3672,10 +3927,10 @@
         <v>14709</v>
       </c>
       <c r="B62" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C62" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D62" t="s">
         <v>9</v>
@@ -3684,10 +3939,10 @@
         <v>10</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G62" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3695,10 +3950,10 @@
         <v>14724</v>
       </c>
       <c r="B63" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C63" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D63" t="s">
         <v>9</v>
@@ -3707,10 +3962,10 @@
         <v>15</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G63" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3718,10 +3973,10 @@
         <v>14734</v>
       </c>
       <c r="B64" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C64" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D64" t="s">
         <v>97</v>
@@ -3730,10 +3985,10 @@
         <v>10</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G64" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3741,10 +3996,10 @@
         <v>14744</v>
       </c>
       <c r="B65" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C65" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D65" t="s">
         <v>9</v>
@@ -3753,10 +4008,10 @@
         <v>15</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G65" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3764,10 +4019,10 @@
         <v>14753</v>
       </c>
       <c r="B66" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C66" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D66" t="s">
         <v>97</v>
@@ -3776,10 +4031,10 @@
         <v>15</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G66" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3787,10 +4042,10 @@
         <v>14764</v>
       </c>
       <c r="B67" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C67" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D67" t="s">
         <v>97</v>
@@ -3799,10 +4054,10 @@
         <v>15</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G67" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3810,10 +4065,10 @@
         <v>14772</v>
       </c>
       <c r="B68" t="s">
-        <v>606</v>
+        <v>275</v>
       </c>
       <c r="C68" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
@@ -3822,10 +4077,10 @@
         <v>15</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>607</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3833,10 +4088,10 @@
         <v>14781</v>
       </c>
       <c r="B69" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C69" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D69" t="s">
         <v>97</v>
@@ -3845,10 +4100,10 @@
         <v>15</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G69" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3856,10 +4111,10 @@
         <v>14790</v>
       </c>
       <c r="B70" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C70" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
@@ -3868,10 +4123,10 @@
         <v>10</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G70" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3879,10 +4134,10 @@
         <v>14799</v>
       </c>
       <c r="B71" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C71" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D71" t="s">
         <v>9</v>
@@ -3891,10 +4146,10 @@
         <v>15</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G71" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3902,10 +4157,10 @@
         <v>14806</v>
       </c>
       <c r="B72" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C72" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D72" t="s">
         <v>9</v>
@@ -3914,10 +4169,10 @@
         <v>10</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="G72" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3925,10 +4180,10 @@
         <v>14815</v>
       </c>
       <c r="B73" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C73" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D73" t="s">
         <v>9</v>
@@ -3937,10 +4192,10 @@
         <v>10</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G73" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3948,10 +4203,10 @@
         <v>14822</v>
       </c>
       <c r="B74" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C74" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D74" t="s">
         <v>9</v>
@@ -3960,10 +4215,10 @@
         <v>10</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G74" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3971,10 +4226,10 @@
         <v>14832</v>
       </c>
       <c r="B75" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C75" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D75" t="s">
         <v>9</v>
@@ -3983,10 +4238,10 @@
         <v>15</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G75" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -3994,10 +4249,10 @@
         <v>14847</v>
       </c>
       <c r="B76" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C76" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D76" t="s">
         <v>9</v>
@@ -4006,10 +4261,10 @@
         <v>10</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G76" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -4017,10 +4272,10 @@
         <v>14857</v>
       </c>
       <c r="B77" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C77" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D77" t="s">
         <v>9</v>
@@ -4029,10 +4284,10 @@
         <v>10</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G77" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -4040,10 +4295,10 @@
         <v>14875</v>
       </c>
       <c r="B78" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C78" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D78" t="s">
         <v>9</v>
@@ -4052,10 +4307,10 @@
         <v>32</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G78" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -4063,10 +4318,10 @@
         <v>14885</v>
       </c>
       <c r="B79" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C79" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D79" t="s">
         <v>9</v>
@@ -4075,10 +4330,10 @@
         <v>32</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G79" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -4086,10 +4341,10 @@
         <v>14894</v>
       </c>
       <c r="B80" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C80" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
@@ -4098,10 +4353,10 @@
         <v>32</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G80" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -4109,10 +4364,10 @@
         <v>14905</v>
       </c>
       <c r="B81" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C81" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D81" t="s">
         <v>9</v>
@@ -4121,10 +4376,10 @@
         <v>15</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G81" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4132,10 +4387,10 @@
         <v>14914</v>
       </c>
       <c r="B82" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C82" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
@@ -4144,10 +4399,10 @@
         <v>15</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G82" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -4155,10 +4410,10 @@
         <v>14924</v>
       </c>
       <c r="B83" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C83" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
@@ -4167,10 +4422,10 @@
         <v>15</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G83" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -4178,10 +4433,10 @@
         <v>14936</v>
       </c>
       <c r="B84" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C84" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D84" t="s">
         <v>9</v>
@@ -4190,10 +4445,10 @@
         <v>15</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G84" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -4201,10 +4456,10 @@
         <v>14945</v>
       </c>
       <c r="B85" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C85" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D85" t="s">
         <v>97</v>
@@ -4213,10 +4468,10 @@
         <v>15</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="G85" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -4224,10 +4479,10 @@
         <v>14953</v>
       </c>
       <c r="B86" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C86" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D86" t="s">
         <v>9</v>
@@ -4236,10 +4491,10 @@
         <v>15</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="G86" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -4247,10 +4502,10 @@
         <v>14961</v>
       </c>
       <c r="B87" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C87" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D87" t="s">
         <v>97</v>
@@ -4259,10 +4514,10 @@
         <v>10</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G87" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -4270,10 +4525,10 @@
         <v>15123</v>
       </c>
       <c r="B88" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C88" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D88" t="s">
         <v>9</v>
@@ -4282,10 +4537,10 @@
         <v>15</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G88" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -4293,10 +4548,10 @@
         <v>15131</v>
       </c>
       <c r="B89" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C89" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D89" t="s">
         <v>9</v>
@@ -4305,10 +4560,10 @@
         <v>32</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G89" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -4316,10 +4571,10 @@
         <v>15138</v>
       </c>
       <c r="B90" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C90" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D90" t="s">
         <v>97</v>
@@ -4328,10 +4583,10 @@
         <v>15</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G90" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -4339,10 +4594,10 @@
         <v>15149</v>
       </c>
       <c r="B91" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C91" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D91" t="s">
         <v>97</v>
@@ -4351,10 +4606,10 @@
         <v>32</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G91" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -4365,7 +4620,7 @@
         <v>59</v>
       </c>
       <c r="C92" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D92" t="s">
         <v>9</v>
@@ -4374,10 +4629,10 @@
         <v>32</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G92" t="s">
-        <v>62</v>
+        <v>373</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -4385,10 +4640,10 @@
         <v>15170</v>
       </c>
       <c r="B93" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C93" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D93" t="s">
         <v>9</v>
@@ -4397,10 +4652,10 @@
         <v>10</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="G93" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -4408,10 +4663,10 @@
         <v>15178</v>
       </c>
       <c r="B94" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C94" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D94" t="s">
         <v>9</v>
@@ -4420,10 +4675,10 @@
         <v>15</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G94" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -4431,10 +4686,10 @@
         <v>15187</v>
       </c>
       <c r="B95" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C95" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D95" t="s">
         <v>9</v>
@@ -4443,10 +4698,10 @@
         <v>10</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="G95" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -4454,10 +4709,10 @@
         <v>15193</v>
       </c>
       <c r="B96" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C96" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D96" t="s">
         <v>9</v>
@@ -4466,10 +4721,10 @@
         <v>32</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="G96" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -4477,10 +4732,10 @@
         <v>15200</v>
       </c>
       <c r="B97" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C97" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
@@ -4489,10 +4744,10 @@
         <v>15</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="G97" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4500,10 +4755,10 @@
         <v>15207</v>
       </c>
       <c r="B98" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C98" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
@@ -4512,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="G98" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -4523,10 +4778,10 @@
         <v>15216</v>
       </c>
       <c r="B99" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C99" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
@@ -4535,10 +4790,10 @@
         <v>10</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G99" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -4546,10 +4801,10 @@
         <v>15224</v>
       </c>
       <c r="B100" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C100" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D100" t="s">
         <v>9</v>
@@ -4558,10 +4813,10 @@
         <v>15</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="G100" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -4569,10 +4824,10 @@
         <v>15230</v>
       </c>
       <c r="B101" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C101" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D101" t="s">
         <v>9</v>
@@ -4581,10 +4836,10 @@
         <v>10</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="G101" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -4592,10 +4847,10 @@
         <v>15238</v>
       </c>
       <c r="B102" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C102" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D102" t="s">
         <v>9</v>
@@ -4604,10 +4859,10 @@
         <v>15</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="G102" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -4615,10 +4870,10 @@
         <v>15246</v>
       </c>
       <c r="B103" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C103" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="D103" t="s">
         <v>97</v>
@@ -4627,10 +4882,10 @@
         <v>10</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="G103" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -4638,10 +4893,10 @@
         <v>15255</v>
       </c>
       <c r="B104" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C104" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D104" t="s">
         <v>9</v>
@@ -4650,10 +4905,10 @@
         <v>10</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G104" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -4661,10 +4916,10 @@
         <v>15263</v>
       </c>
       <c r="B105" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C105" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D105" t="s">
         <v>9</v>
@@ -4673,10 +4928,10 @@
         <v>10</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="G105" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4684,10 +4939,10 @@
         <v>15272</v>
       </c>
       <c r="B106" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C106" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D106" t="s">
         <v>9</v>
@@ -4696,10 +4951,10 @@
         <v>32</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="G106" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4707,10 +4962,10 @@
         <v>15279</v>
       </c>
       <c r="B107" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C107" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D107" t="s">
         <v>9</v>
@@ -4719,10 +4974,10 @@
         <v>10</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="G107" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4730,10 +4985,10 @@
         <v>15287</v>
       </c>
       <c r="B108" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C108" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D108" t="s">
         <v>9</v>
@@ -4742,10 +4997,10 @@
         <v>10</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="G108" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4753,10 +5008,10 @@
         <v>15300</v>
       </c>
       <c r="B109" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C109" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="D109" t="s">
         <v>9</v>
@@ -4765,10 +5020,10 @@
         <v>10</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G109" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4776,10 +5031,10 @@
         <v>15308</v>
       </c>
       <c r="B110" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C110" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D110" t="s">
         <v>97</v>
@@ -4788,10 +5043,10 @@
         <v>15</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="G110" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -4799,10 +5054,10 @@
         <v>15316</v>
       </c>
       <c r="B111" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C111" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D111" t="s">
         <v>97</v>
@@ -4811,10 +5066,10 @@
         <v>15</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="G111" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -4822,10 +5077,10 @@
         <v>15324</v>
       </c>
       <c r="B112" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C112" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D112" t="s">
         <v>97</v>
@@ -4834,10 +5089,10 @@
         <v>10</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="G112" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -4845,10 +5100,10 @@
         <v>15334</v>
       </c>
       <c r="B113" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C113" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D113" t="s">
         <v>97</v>
@@ -4857,10 +5112,10 @@
         <v>15</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="G113" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -4868,10 +5123,10 @@
         <v>15348</v>
       </c>
       <c r="B114" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C114" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D114" t="s">
         <v>97</v>
@@ -4880,10 +5135,10 @@
         <v>15</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="G114" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -4891,10 +5146,10 @@
         <v>15358</v>
       </c>
       <c r="B115" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C115" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D115" t="s">
         <v>9</v>
@@ -4903,10 +5158,10 @@
         <v>32</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="G115" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4914,10 +5169,10 @@
         <v>15366</v>
       </c>
       <c r="B116" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C116" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D116" t="s">
         <v>9</v>
@@ -4926,10 +5181,10 @@
         <v>10</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="G116" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -4937,10 +5192,10 @@
         <v>15375</v>
       </c>
       <c r="B117" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C117" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D117" t="s">
         <v>9</v>
@@ -4949,10 +5204,10 @@
         <v>10</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="G117" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4960,10 +5215,10 @@
         <v>15383</v>
       </c>
       <c r="B118" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C118" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D118" t="s">
         <v>9</v>
@@ -4972,10 +5227,10 @@
         <v>15</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G118" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -4983,10 +5238,10 @@
         <v>15394</v>
       </c>
       <c r="B119" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C119" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D119" t="s">
         <v>9</v>
@@ -4995,10 +5250,10 @@
         <v>15</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="G119" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -5006,10 +5261,10 @@
         <v>15646</v>
       </c>
       <c r="B120" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C120" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D120" t="s">
         <v>9</v>
@@ -5018,10 +5273,10 @@
         <v>10</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="G120" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -5029,10 +5284,10 @@
         <v>15667</v>
       </c>
       <c r="B121" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C121" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D121" t="s">
         <v>9</v>
@@ -5041,21 +5296,21 @@
         <v>10</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="G121" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>15741</v>
+        <v>15678</v>
       </c>
       <c r="B122" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C122" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D122" t="s">
         <v>9</v>
@@ -5064,21 +5319,21 @@
         <v>10</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="G122" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>15751</v>
+        <v>15689</v>
       </c>
       <c r="B123" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C123" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D123" t="s">
         <v>9</v>
@@ -5087,21 +5342,21 @@
         <v>10</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="G123" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>15759</v>
+        <v>15741</v>
       </c>
       <c r="B124" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C124" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D124" t="s">
         <v>9</v>
@@ -5110,21 +5365,21 @@
         <v>10</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="G124" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>15769</v>
+        <v>15751</v>
       </c>
       <c r="B125" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C125" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
@@ -5133,21 +5388,21 @@
         <v>10</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="G125" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>15778</v>
+        <v>15759</v>
       </c>
       <c r="B126" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C126" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D126" t="s">
         <v>9</v>
@@ -5156,182 +5411,182 @@
         <v>10</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="G126" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>15787</v>
+        <v>15769</v>
       </c>
       <c r="B127" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C127" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D127" t="s">
         <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="G127" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>15795</v>
+        <v>15778</v>
       </c>
       <c r="B128" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C128" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D128" t="s">
         <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="G128" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>15806</v>
+        <v>15787</v>
       </c>
       <c r="B129" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C129" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="D129" t="s">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="G129" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>15819</v>
+        <v>15795</v>
       </c>
       <c r="B130" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C130" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="D130" t="s">
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="G130" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>15828</v>
+        <v>15806</v>
       </c>
       <c r="B131" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C131" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="D131" t="s">
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="G131" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>15838</v>
+        <v>15819</v>
       </c>
       <c r="B132" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C132" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="D132" t="s">
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="G132" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>15848</v>
+        <v>15828</v>
       </c>
       <c r="B133" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C133" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="D133" t="s">
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="G133" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>15855</v>
+        <v>15838</v>
       </c>
       <c r="B134" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C134" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="D134" t="s">
         <v>9</v>
@@ -5340,21 +5595,21 @@
         <v>32</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="G134" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>15863</v>
+        <v>15848</v>
       </c>
       <c r="B135" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C135" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="D135" t="s">
         <v>9</v>
@@ -5363,67 +5618,67 @@
         <v>32</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="G135" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>15872</v>
+        <v>15855</v>
       </c>
       <c r="B136" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C136" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="D136" t="s">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="G136" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>15880</v>
+        <v>15863</v>
       </c>
       <c r="B137" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C137" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D137" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="G137" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>15891</v>
+        <v>15872</v>
       </c>
       <c r="B138" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C138" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D138" t="s">
         <v>9</v>
@@ -5432,21 +5687,21 @@
         <v>10</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="G138" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>15900</v>
+        <v>15880</v>
       </c>
       <c r="B139" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C139" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D139" t="s">
         <v>97</v>
@@ -5455,90 +5710,90 @@
         <v>10</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="G139" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>15909</v>
+        <v>15891</v>
       </c>
       <c r="B140" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C140" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D140" t="s">
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="G140" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>15918</v>
+        <v>15900</v>
       </c>
       <c r="B141" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C141" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D141" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="G141" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>15926</v>
+        <v>15909</v>
       </c>
       <c r="B142" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C142" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D142" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="G142" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>15937</v>
+        <v>15918</v>
       </c>
       <c r="B143" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C143" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="D143" t="s">
         <v>9</v>
@@ -5547,67 +5802,67 @@
         <v>10</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="G143" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>15945</v>
+        <v>15926</v>
       </c>
       <c r="B144" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C144" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D144" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="E144" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="G144" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>15955</v>
+        <v>15937</v>
       </c>
       <c r="B145" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C145" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D145" t="s">
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="G145" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>15968</v>
+        <v>15945</v>
       </c>
       <c r="B146" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C146" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D146" t="s">
         <v>9</v>
@@ -5616,21 +5871,21 @@
         <v>32</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="G146" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>15976</v>
+        <v>15955</v>
       </c>
       <c r="B147" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C147" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D147" t="s">
         <v>9</v>
@@ -5639,21 +5894,21 @@
         <v>32</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="G147" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>16003</v>
+        <v>15968</v>
       </c>
       <c r="B148" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C148" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="D148" t="s">
         <v>9</v>
@@ -5662,44 +5917,44 @@
         <v>32</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="G148" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>16012</v>
+        <v>15976</v>
       </c>
       <c r="B149" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C149" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D149" t="s">
         <v>9</v>
       </c>
       <c r="E149" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="G149" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>16020</v>
+        <v>16003</v>
       </c>
       <c r="B150" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C150" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D150" t="s">
         <v>9</v>
@@ -5708,21 +5963,21 @@
         <v>32</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="G150" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>16022</v>
+        <v>16012</v>
       </c>
       <c r="B151" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C151" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D151" t="s">
         <v>9</v>
@@ -5731,173 +5986,781 @@
         <v>15</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="G151" s="5" t="s">
-        <v>604</v>
+        <v>608</v>
+      </c>
+      <c r="G151" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>16020</v>
+      </c>
+      <c r="B152" t="s">
+        <v>610</v>
+      </c>
+      <c r="C152" t="s">
+        <v>611</v>
+      </c>
+      <c r="D152" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" t="s">
+        <v>32</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="G152" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>16022</v>
+      </c>
+      <c r="B153" t="s">
+        <v>614</v>
+      </c>
+      <c r="C153" t="s">
+        <v>615</v>
+      </c>
+      <c r="D153" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" t="s">
+        <v>15</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>618</v>
+      </c>
+      <c r="C154" t="s">
+        <v>619</v>
+      </c>
+      <c r="D154" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" t="s">
+        <v>10</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>622</v>
+      </c>
+      <c r="C155" t="s">
+        <v>623</v>
+      </c>
+      <c r="D155" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" t="s">
+        <v>32</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>626</v>
+      </c>
+      <c r="C156" t="s">
+        <v>627</v>
+      </c>
+      <c r="D156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" t="s">
+        <v>15</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>630</v>
+      </c>
+      <c r="C157" t="s">
+        <v>631</v>
+      </c>
+      <c r="D157" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" t="s">
+        <v>10</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B158" t="s">
+        <v>634</v>
+      </c>
+      <c r="C158" t="s">
+        <v>635</v>
+      </c>
+      <c r="D158" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" t="s">
+        <v>15</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>638</v>
+      </c>
+      <c r="C159" t="s">
+        <v>639</v>
+      </c>
+      <c r="D159" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" t="s">
+        <v>15</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>642</v>
+      </c>
+      <c r="C160" t="s">
+        <v>643</v>
+      </c>
+      <c r="D160" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" t="s">
+        <v>15</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>646</v>
+      </c>
+      <c r="C161" t="s">
+        <v>647</v>
+      </c>
+      <c r="D161" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" t="s">
+        <v>10</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="162" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>650</v>
+      </c>
+      <c r="C162" t="s">
+        <v>651</v>
+      </c>
+      <c r="D162" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" t="s">
+        <v>10</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="163" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>654</v>
+      </c>
+      <c r="C163" t="s">
+        <v>655</v>
+      </c>
+      <c r="D163" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" t="s">
+        <v>10</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="164" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>658</v>
+      </c>
+      <c r="C164" t="s">
+        <v>659</v>
+      </c>
+      <c r="D164" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" t="s">
+        <v>10</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="G164" s="5" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="165" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>662</v>
+      </c>
+      <c r="C165" t="s">
+        <v>663</v>
+      </c>
+      <c r="D165" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" t="s">
+        <v>10</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="166" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
+        <v>666</v>
+      </c>
+      <c r="C166" t="s">
+        <v>667</v>
+      </c>
+      <c r="D166" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" t="s">
+        <v>10</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="167" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
+        <v>670</v>
+      </c>
+      <c r="C167" t="s">
+        <v>671</v>
+      </c>
+      <c r="D167" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" t="s">
+        <v>15</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="168" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>674</v>
+      </c>
+      <c r="C168" t="s">
+        <v>675</v>
+      </c>
+      <c r="D168" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" t="s">
+        <v>32</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="169" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
+        <v>678</v>
+      </c>
+      <c r="C169" t="s">
+        <v>679</v>
+      </c>
+      <c r="D169" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" t="s">
+        <v>10</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="170" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B170" t="s">
+        <v>682</v>
+      </c>
+      <c r="C170" t="s">
+        <v>683</v>
+      </c>
+      <c r="D170" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" t="s">
+        <v>15</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="171" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
+        <v>686</v>
+      </c>
+      <c r="C171" t="s">
+        <v>687</v>
+      </c>
+      <c r="D171" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" t="s">
+        <v>10</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="172" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B172" t="s">
+        <v>690</v>
+      </c>
+      <c r="C172" t="s">
+        <v>691</v>
+      </c>
+      <c r="D172" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" t="s">
+        <v>15</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>693</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F151" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F172" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="F6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="F8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="F9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="F10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="F11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="F12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="F13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="F14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="F15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="F17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="F23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="F25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="F26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="F27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="F28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="F30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="F31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="F32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="F33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="F34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="F35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="F36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="F37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="F38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="F39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="F40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="F41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="F42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="F43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="F44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="F45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="F46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="F47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="F48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="F49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="F50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="F51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="F52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="F53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="F54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="F55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="F56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="F57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="F58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="F59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="F60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="F61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="F62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="F63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="F64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="F65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="F66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="F67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="F68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="F69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="F70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="F71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="F72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="F73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="F74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="F75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="F76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="F77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="F78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="F79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="F80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="F81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="F82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="F83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="F84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="F85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="F86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="F87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="F88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="F89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="F90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="F91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="F92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="F93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="F94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="F95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="F96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="F97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="F98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="F99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="F100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="F101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="F102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="F103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="F104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="F105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="F106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="F107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="F108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="F109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="F110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="F111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="F112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="F113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="F114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="F115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="F116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="F117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="F118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="F119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="F120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="F121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="F122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="F123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="F124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="F125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="F126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="F127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="F128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="F129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="F130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="F131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="F132" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="F133" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="F134" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="F135" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="F136" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="F137" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="F138" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="F139" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="F140" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="F141" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="F142" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="F143" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="F144" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="F145" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="F146" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="F147" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="F148" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="F149" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="F150" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="F151" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="G2" r:id="rId151" xr:uid="{2127BB33-F9D5-4B31-91B2-3263907C5E32}"/>
-    <hyperlink ref="G3" r:id="rId152" xr:uid="{639AE796-07CD-4949-B046-5ABBDDC04F27}"/>
-    <hyperlink ref="G151" r:id="rId153" xr:uid="{74F8BE39-9930-4455-B3D9-F6F1F0643748}"/>
-    <hyperlink ref="G68" r:id="rId154" xr:uid="{EFB8BA38-8B68-4359-8AB1-4EA6D31172E9}"/>
-    <hyperlink ref="G32" r:id="rId155" xr:uid="{92990900-070E-4439-9C9C-214DAEF8CF22}"/>
-    <hyperlink ref="G15" r:id="rId156" xr:uid="{9FB85190-16BC-43A5-985B-8CE12A847691}"/>
-    <hyperlink ref="G59" r:id="rId157" xr:uid="{26747CAA-0C2B-4412-988E-F35D36BF76AD}"/>
-    <hyperlink ref="G4" r:id="rId158" xr:uid="{93090924-BC40-46F7-ABC7-EA5F24F80CC7}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F4" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="G4" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F5" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="G5" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="F6" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="G6" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F7" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="G7" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="F8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="G8" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="G9" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F10" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="G10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="F11" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="G11" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="F12" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="G12" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="F13" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="G13" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="F14" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="G14" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="F15" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="G15" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="F16" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="G16" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F17" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="G17" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="F18" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="G18" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="F19" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="G19" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="F20" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="G20" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="F21" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="G21" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="F22" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="G22" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="F23" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="G23" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="F24" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="G24" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="F25" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="G25" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="F26" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="G26" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="F27" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="G27" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="F28" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="G28" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="F29" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="G29" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="F30" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="G30" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="F31" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="G31" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="F32" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="G32" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F33" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="G33" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="F34" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="G34" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="F35" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="G35" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="F36" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="G36" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="F37" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="G37" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="F38" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="G38" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="F39" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="G39" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="F40" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="G40" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="F41" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="G41" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="F42" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="G42" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="F43" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="G43" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="F44" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="G44" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="F45" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="G45" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="F46" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="G46" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="F47" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="G47" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="F48" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="G48" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="F49" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="G49" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="F50" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="G50" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="F51" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="G51" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="F52" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="G52" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="F53" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="G53" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="F54" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="G54" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="F55" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="G55" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="F56" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="G56" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="F57" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="G57" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="F58" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="G58" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="F59" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="G59" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="F60" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="G60" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="F61" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="G61" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="F62" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="G62" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="F63" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="G63" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="F64" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="G64" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="F65" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="G65" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="F66" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="G66" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="F67" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="G67" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="F68" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="G68" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="F69" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="G69" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="F70" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="G70" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="F71" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="G71" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="F72" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="G72" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="F73" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="G73" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="F74" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="G74" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="F75" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="G75" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="F76" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="G76" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="F77" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="G77" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="F78" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="G78" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="F79" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="G79" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="F80" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="G80" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="F81" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="G81" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="F82" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="G82" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="F83" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="G83" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="F84" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="G84" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="F85" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="G85" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="F86" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="G86" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="F87" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="G87" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="F88" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="G88" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="F89" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="G89" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="F90" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="G90" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="F91" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="G91" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="F92" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="G92" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="F93" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="G93" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="F94" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="G94" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="F95" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="G95" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="F96" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="G96" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="F97" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="G97" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="F98" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="G98" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="F99" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="G99" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="F100" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="G100" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="F101" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="G101" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="F102" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="G102" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="F103" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="G103" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="F104" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="G104" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="F105" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="G105" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="F106" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="G106" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="F107" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="G107" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="F108" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="G108" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="F109" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="G109" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="F110" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="G110" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="F111" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="G111" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="F112" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="G112" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="F113" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="G113" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="F114" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="G114" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="F115" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="G115" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="F116" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="G116" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="F117" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="G117" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="F118" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="G118" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="F119" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="G119" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="F120" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="G120" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="F121" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="G121" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="F122" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="F123" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="F124" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="G124" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="F125" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="G125" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="F126" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="G126" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="F127" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="G127" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="F128" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="G128" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="F129" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="G129" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="F130" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="G130" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="F131" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="G131" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="F132" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="G132" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="F133" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="G133" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="F134" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="G134" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="F135" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="G135" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="F136" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="G136" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="F137" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="G137" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="F138" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="G138" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="F139" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="G139" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="F140" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="G140" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="F141" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="G141" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="F142" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="G142" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="F143" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="G143" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="F144" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="G144" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="F145" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="G145" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="F146" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="G146" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="F147" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="G147" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="F148" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="G148" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="F149" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="G149" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="F150" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="G150" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="F151" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="G151" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="F152" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="G152" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="F153" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="G153" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="F154" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="G154" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="F155" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="G155" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="F156" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="G156" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="F157" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="G157" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="F158" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="G158" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="F159" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="G159" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="F160" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="G160" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="F161" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="G161" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="F162" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="G162" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="F163" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="G163" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="F164" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="G164" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="F165" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="G165" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="F166" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="G166" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="F167" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="G167" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="F168" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="G168" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="F169" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="G169" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="F170" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="G170" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="F171" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="G171" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="F172" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="G172" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
